--- a/resources/table/enum.board.xlsx
+++ b/resources/table/enum.board.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cshyeon\fb\resources\table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cshyeon\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC7F1014-D928-464B-9AA7-992B6C7E8E72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62648349-31B1-4B1A-BEC0-5136BC5C86FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17790" xr2:uid="{E3DF90E4-1439-4BA6-8481-C5727015A5CB}"/>
+    <workbookView xWindow="28680" yWindow="-180" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E3DF90E4-1439-4BA6-8481-C5727015A5CB}"/>
   </bookViews>
   <sheets>
     <sheet name="BOARD_ACTION" sheetId="1" r:id="rId1"/>
     <sheet name="BOARD_BUTTON_ENABLE" sheetId="2" r:id="rId2"/>
+    <sheet name="MAIL_BUTTON_ENABLE" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
   <si>
     <t>0x01</t>
   </si>
@@ -68,6 +69,38 @@
   </si>
   <si>
     <t>0x04</t>
+  </si>
+  <si>
+    <t>SEND_MAIL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x06</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MAIL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x09</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NONE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NEW</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -476,7 +509,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF0AC299-6373-444B-B465-F5D3A155A1B8}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.125" style="1" bestFit="1" customWidth="1"/>
@@ -529,6 +562,22 @@
       </c>
       <c r="B6" s="1" t="s">
         <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -581,4 +630,34 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3845240-DAB3-4801-97AA-55B068DB2EBB}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="16384" width="9" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>